--- a/Outputs/Scenarios/PtX_demand_PT_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_PT_Electrification.xlsx
@@ -1975,7 +1975,7 @@
         <v>2050</v>
       </c>
       <c r="C42" t="n">
-        <v>0.001424875712682911</v>
+        <v>0.001424875712682912</v>
       </c>
       <c r="D42" t="n">
         <v>0.001133679841243609</v>

--- a/Outputs/Scenarios/PtX_demand_PT_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_PT_Electrification.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.0004653717633502872</v>
       </c>
       <c r="K16" t="n">
-        <v>0.003036598292467713</v>
+        <v>0.003243106961512187</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0005060997154112855</v>
+        <v>0.0006694236335349222</v>
       </c>
     </row>
     <row r="18">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.002024398861645142</v>
+        <v>0.002677694534139689</v>
       </c>
     </row>
     <row r="19">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.003036598292467713</v>
+        <v>0.002677694534139689</v>
       </c>
     </row>
     <row r="20">
@@ -1333,7 +1333,7 @@
         <v>3.72949799024412e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>0.004207841176031449</v>
+        <v>0.0041310794129683</v>
       </c>
     </row>
     <row r="25">
@@ -1370,7 +1370,7 @@
         <v>0.0002257465918113596</v>
       </c>
       <c r="K25" t="n">
-        <v>0.04115579008516783</v>
+        <v>0.04040500342877271</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>6.705219367598594e-06</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0005060997154112855</v>
+        <v>0.0006694236335349222</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.0006889262383035935</v>
       </c>
       <c r="K30" t="n">
-        <v>0.01787424780398671</v>
+        <v>0.0175000789707683</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.002979041300664452</v>
+        <v>0.003612266444119184</v>
       </c>
     </row>
     <row r="32">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.01191616520265781</v>
+        <v>0.01444906577647673</v>
       </c>
     </row>
     <row r="33">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.01787424780398671</v>
+        <v>0.01444906577647673</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>3.625927570018914e-05</v>
       </c>
       <c r="K42" t="n">
-        <v>0.002979041300664452</v>
+        <v>0.003612266444119184</v>
       </c>
     </row>
     <row r="43">
